--- a/www/download/IND.gross_output.s.du.rpA2.xlsx
+++ b/www/download/IND.gross_output.s.du.rpA2.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 2</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.161</t>
+          <t>161218.891278027</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.166</t>
+          <t>165721.682198757</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.164</t>
+          <t>163924.106318827</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0.164</t>
+          <t>163526.892187366</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.181</t>
+          <t>180674.859435081</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.179</t>
+          <t>179369.813796989</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>170132.945713529</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.184</t>
+          <t>183794.920944779</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.208</t>
+          <t>207961.968371218</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0.251</t>
+          <t>250798.509500737</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>0.276</t>
+          <t>275516.585840864</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>0.293</t>
+          <t>293467.806849664</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>0.346</t>
+          <t>346271.137100725</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>399607.361419817</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>0.381</t>
+          <t>381184.266828478</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,84 +775,84 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>95306.0249131874</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.099</t>
+          <t>98578.2719403453</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.092</t>
+          <t>91980.9708322064</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>93196.5899966647</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0.098</t>
+          <t>98008.8938112774</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.103</t>
+          <t>103078.015731516</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.103</t>
+          <t>102646.67113865</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.103</t>
+          <t>103374.730495597</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>113855.783921344</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>131569.78215017</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>138501.483005859</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>0.154</t>
+          <t>153953.408157673</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>0.177</t>
+          <t>177245.232685373</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>0.181</t>
+          <t>180917.125500312</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>0.148</t>
+          <t>147746.858552293</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.108</t>
+          <t>108208.767161476</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.103</t>
+          <t>103461.844139846</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>97118.1927747096</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.098</t>
+          <t>98019.2941700692</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.104</t>
+          <t>104170.997456941</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.115</t>
+          <t>114685.714599094</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.111</t>
+          <t>111203.865645677</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.111</t>
+          <t>110543.757862824</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.128</t>
+          <t>127995.021198717</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>149694.832079969</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.156</t>
+          <t>155715.045545528</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.175</t>
+          <t>174516.951096672</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.204</t>
+          <t>204319.429938507</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.262</t>
+          <t>261924.98753764</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.188</t>
+          <t>187997.271054275</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>53770.2075302608</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>56026.3619418727</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>48854.6992773104</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>45099.2605893854</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>46455.8190836902</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>42191.2846063765</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>38310.2153554819</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>38324.8559314877</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>43735.5112309058</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>52069.9419979081</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>56326.6979112254</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>63946.7995470471</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>0.076</t>
+          <t>75859.3020529106</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>86753.9284951824</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>0.081</t>
+          <t>80539.2487442107</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.073</t>
+          <t>1073143.42123088</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.076</t>
+          <t>1075693.85196203</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1070307.01610797</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1.047</t>
+          <t>1047434.77834948</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1.116</t>
+          <t>1115732.78585875</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1.187</t>
+          <t>1186822.9968532</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1.141</t>
+          <t>1141011.67057857</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>1.204</t>
+          <t>1203949.9090671</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>1.347</t>
+          <t>1346659.30812357</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>1.557</t>
+          <t>1556843.80600535</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>1.718</t>
+          <t>1718465.44942581</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>1.832</t>
+          <t>1832357.68148712</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>2.158</t>
+          <t>2157562.89387592</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2.501</t>
+          <t>2500907.3324096</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2.276</t>
+          <t>2275853.98292366</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.303</t>
+          <t>303122.816303607</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.309</t>
+          <t>309459.573126782</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.306</t>
+          <t>305522.213036468</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0.305</t>
+          <t>305090.457102355</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0.331</t>
+          <t>331448.936096928</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.365</t>
+          <t>364739.14175431</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.354</t>
+          <t>354158.553183297</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>0.349</t>
+          <t>349168.912235744</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>0.388</t>
+          <t>388070.95843958</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0.456</t>
+          <t>456021.287855829</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>500212.240726103</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>0.538</t>
+          <t>537652.052021564</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>0.592</t>
+          <t>591924.158727582</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>0.659</t>
+          <t>658702.092015314</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>0.573</t>
+          <t>573123.612707858</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>11.695</t>
+          <t>11694623.5000782</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>12.153</t>
+          <t>12152799.1521885</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>12.17</t>
+          <t>12169789.8710391</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>11.923</t>
+          <t>11923066.7518554</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>12.286</t>
+          <t>12285549.6084018</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>12.275</t>
+          <t>12274929.4347477</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>12.071</t>
+          <t>12071142.915067</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>12.473</t>
+          <t>12473058.9427216</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>14.242</t>
+          <t>14241757.314865</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>16.016</t>
+          <t>16016105.2206999</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>18.25</t>
+          <t>18249755.6111807</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>21.354</t>
+          <t>21353869.1272079</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>25.129</t>
+          <t>25128599.084984</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>29.133</t>
+          <t>29132721.1143872</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>27.459</t>
+          <t>27459240.2876982</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,84 +1297,84 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>6179.52987097817</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>6595.88791435846</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>5874.29922152375</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>5776.35759467558</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>6503.35546035525</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>6615.26423363658</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>6970.16000755571</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>7376.94537877503</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>8226.56792604774</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>8512.25800780879</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>8304.96201562416</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>8876.81069149839</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>10056.1010687471</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>14329.6012950119</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>9486.30057986138</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,84 +1384,84 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>149907.894585682</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.153</t>
+          <t>152873.950971375</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.153</t>
+          <t>153238.708203469</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>0.146</t>
+          <t>145776.785703306</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0.145</t>
+          <t>145443.834614052</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.141</t>
+          <t>141097.748710287</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>139041.726619167</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0.143</t>
+          <t>143087.567736812</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>0.152</t>
+          <t>152379.047904111</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>169675.434304433</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>0.182</t>
+          <t>182479.557070317</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>0.204</t>
+          <t>203602.339824506</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>0.235</t>
+          <t>235187.011931841</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>0.251</t>
+          <t>250942.296949602</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>0.199</t>
+          <t>198528.163606685</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,84 +1471,84 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.947</t>
+          <t>947084.366490825</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.883</t>
+          <t>882616.740907669</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.828</t>
+          <t>828028.323375597</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>0.859</t>
+          <t>859024.066239171</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>0.898</t>
+          <t>898055.144550991</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.946</t>
+          <t>946460.618162972</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.883</t>
+          <t>883495.026759544</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>0.879</t>
+          <t>879137.208171044</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>1.003</t>
+          <t>1003350.01911137</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>1.137</t>
+          <t>1136984.9334222</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>1.191</t>
+          <t>1191076.8778607</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>1.298</t>
+          <t>1298067.41011083</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>1.519</t>
+          <t>1519036.07128753</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>1.519</t>
+          <t>1519009.37603552</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>1.219</t>
+          <t>1219286.80717446</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,84 +1558,84 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.074</t>
+          <t>74274.8274381842</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.074</t>
+          <t>74117.1636773374</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>77750.5870131175</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>71755.5835959861</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>0.071</t>
+          <t>70882.5436045193</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>72874.3000901089</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>72407.3182993154</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>72866.9117189641</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>82760.693069546</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0.092</t>
+          <t>92390.2021819214</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>97415.9718465329</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>0.104</t>
+          <t>104272.330519276</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>0.116</t>
+          <t>116205.608538753</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>0.122</t>
+          <t>121863.186511018</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>0.099</t>
+          <t>98600.5083699256</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,84 +1645,84 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.298</t>
+          <t>298230.211865156</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>0.308</t>
+          <t>308166.859613611</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.295</t>
+          <t>294922.004418475</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>0.315</t>
+          <t>314670.538796543</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>0.355</t>
+          <t>354799.807609369</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>0.395</t>
+          <t>394588.385385484</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>389840.541875075</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>0.421</t>
+          <t>420962.242171258</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>0.468</t>
+          <t>468212.061107815</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>539844.226576352</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>0.612</t>
+          <t>612327.125080059</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>0.672</t>
+          <t>671711.317298415</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>0.775</t>
+          <t>775250.381087892</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>0.811</t>
+          <t>811464.406950034</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>0.623</t>
+          <t>623059.566353044</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>19207.4226430574</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>18116.1684703722</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>18084.3947788269</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>17775.9796857785</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>16971.990458208</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>18135.5468281755</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>18692.9025559809</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>19755.6647982975</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>22287.7462805065</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>26013.0539827782</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>26364.7867761564</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>28013.838817087</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>29807.882272393</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>31344.0289159728</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>24609.9785130084</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,84 +1819,84 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.076</t>
+          <t>75524.865514501</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>74548.5888817462</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>72656.3398083319</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0.076</t>
+          <t>76184.5468673922</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.084</t>
+          <t>83941.6828239132</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0.085</t>
+          <t>85019.6486859317</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>80096.8491002682</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>0.081</t>
+          <t>81049.9401122525</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>90291.2302442208</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.101</t>
+          <t>101272.923012081</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0.111</t>
+          <t>110781.510026301</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>120411.606082637</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0.138</t>
+          <t>137633.110127005</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0.143</t>
+          <t>143122.277508197</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0.106</t>
+          <t>105714.258152691</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,84 +1906,84 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.499</t>
+          <t>499343.226627715</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.495</t>
+          <t>495467.879088939</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.456</t>
+          <t>455505.685579359</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.469</t>
+          <t>469199.275035692</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.517</t>
+          <t>517357.919089427</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>540242.582947765</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.523</t>
+          <t>523040.636797454</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.519</t>
+          <t>519440.544429076</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.578</t>
+          <t>578000.370167997</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.651</t>
+          <t>651116.437620992</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.709</t>
+          <t>708718.372328205</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.752</t>
+          <t>752343.628736084</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.875</t>
+          <t>875182.853366469</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.908</t>
+          <t>907596.35529456</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>759751.017800588</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,84 +1993,84 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.553</t>
+          <t>552910.182921764</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.561</t>
+          <t>560691.825271222</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.549</t>
+          <t>548642.820041374</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.551</t>
+          <t>551008.4541354</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.575</t>
+          <t>575473.555719006</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.583</t>
+          <t>582736.65490249</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.557</t>
+          <t>557167.772705763</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.564</t>
+          <t>564166.528679855</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.612</t>
+          <t>611933.411822153</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.688</t>
+          <t>687900.840473863</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.758</t>
+          <t>757634.255962146</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.802</t>
+          <t>801952.324158266</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.905</t>
+          <t>905435.795868801</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.902</t>
+          <t>901647.535865511</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>779545.01165873</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>80424.7999649775</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.084</t>
+          <t>83793.7657625142</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>77005.8619094615</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>78179.5076588859</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.082</t>
+          <t>81508.301306058</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>90869.657151841</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.084</t>
+          <t>84311.7409861908</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>87545.4604758691</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>94740.4583203738</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.106</t>
+          <t>105592.975997329</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.112</t>
+          <t>112135.529578435</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.128</t>
+          <t>128021.749488282</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0.145</t>
+          <t>145431.743063438</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0.162</t>
+          <t>162497.154980177</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0.138</t>
+          <t>137983.246681708</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,84 +2167,84 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.117</t>
+          <t>116533.655222227</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>114423.494168259</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.108</t>
+          <t>107785.880289773</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.108</t>
+          <t>108392.032253699</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.122</t>
+          <t>121883.917112801</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>119226.921799071</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.112</t>
+          <t>112302.489757627</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.115</t>
+          <t>114590.783942706</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.124</t>
+          <t>124396.99248384</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.131</t>
+          <t>131265.409427072</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.138</t>
+          <t>138365.390626544</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.145</t>
+          <t>145353.769534796</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.166</t>
+          <t>165816.235336393</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.164</t>
+          <t>163932.889835555</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.141</t>
+          <t>141034.617605004</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.818</t>
+          <t>818468.941954468</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.866</t>
+          <t>865926.640819336</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.844</t>
+          <t>843800.634701336</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.783</t>
+          <t>783280.672345823</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.922</t>
+          <t>921808.2780453</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.994</t>
+          <t>994169.463277069</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.981</t>
+          <t>981293.494782281</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1059743.6490214</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>1.181</t>
+          <t>1181024.2528118</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>1.298</t>
+          <t>1297571.90592997</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1220050.80749952</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>1.248</t>
+          <t>1247614.83760658</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>1.463</t>
+          <t>1463136.58266609</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>1.635</t>
+          <t>1635275.30048256</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>1.592</t>
+          <t>1592202.48989011</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>7.835</t>
+          <t>7834755.97582395</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>8.017</t>
+          <t>8016627.46562274</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>8.114</t>
+          <t>8114329.08190812</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>8.039</t>
+          <t>8038509.5533457</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>8.182</t>
+          <t>8181611.34921359</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>8.688</t>
+          <t>8688248.42912327</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>8.824</t>
+          <t>8823878.83588505</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>8.92</t>
+          <t>8919941.77282624</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>10.373</t>
+          <t>10373075.3023298</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>11.646</t>
+          <t>11645805.067751</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>12.631</t>
+          <t>12631292.1482648</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>13.271</t>
+          <t>13271420.9872416</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>14.648</t>
+          <t>14647965.4300583</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>15.969</t>
+          <t>15968708.8696556</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>15.169</t>
+          <t>15169447.1330057</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,84 +2428,84 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>44035.0488328386</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>45991.0213391292</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>44809.9215846551</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>44816.061167997</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>51371.6384085972</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>55039.4119669865</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>54660.4103354573</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>53749.0735806622</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>62203.18755399</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0.074</t>
+          <t>74133.0393607114</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>0.084</t>
+          <t>83522.2973353305</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>91452.9846377247</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>0.108</t>
+          <t>108327.87273937</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>109200.93425667</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>0.094</t>
+          <t>93603.1317556674</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,84 +2515,84 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>490028.035257268</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>0.497</t>
+          <t>496506.103386738</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>469666.080097466</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>0.487</t>
+          <t>486723.469334024</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>0.521</t>
+          <t>521232.788690617</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>0.562</t>
+          <t>561543.025265601</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.536</t>
+          <t>536248.174714343</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0.547</t>
+          <t>547009.298419486</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>0.619</t>
+          <t>619102.055497315</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0.705</t>
+          <t>704807.995828407</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>0.756</t>
+          <t>756179.010400663</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>0.856</t>
+          <t>856146.304847407</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>0.972</t>
+          <t>972065.694908132</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>0.966</t>
+          <t>965826.079785142</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>740411.622442741</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2.124</t>
+          <t>2124196.65238359</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2.062</t>
+          <t>2062352.47989845</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.986</t>
+          <t>1986243.22800134</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1820198.34305419</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>1.933</t>
+          <t>1932753.70321303</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2.041</t>
+          <t>2041323.81122767</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1.929</t>
+          <t>1929443.24215544</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>1.889</t>
+          <t>1889358.39252717</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2.094</t>
+          <t>2094198.37231522</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2.378</t>
+          <t>2377818.50152718</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2.541</t>
+          <t>2540897.08784907</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>2.723</t>
+          <t>2723301.23046373</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>3.035</t>
+          <t>3034586.21703312</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>3.443</t>
+          <t>3442849.39434147</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2.736</t>
+          <t>2736307.1767071</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>0.955</t>
+          <t>955164.012042152</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>0.969</t>
+          <t>968591.550897304</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0.948</t>
+          <t>948109.703794028</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>0.858</t>
+          <t>857562.247487237</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>0.954</t>
+          <t>954044.773244941</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>1.035</t>
+          <t>1034659.11970666</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.993</t>
+          <t>992775.766373758</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>1.034</t>
+          <t>1034427.27085587</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>1.143</t>
+          <t>1143204.02741234</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>1.344</t>
+          <t>1344199.09147904</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>1.429</t>
+          <t>1429458.14931501</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>1.553</t>
+          <t>1553252.29152376</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>1.729</t>
+          <t>1728617.36128132</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>1.947</t>
+          <t>1947145.92314696</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>1.718</t>
+          <t>1718380.93685685</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>40115.6918790942</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>38895.6955080076</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>35026.9863715458</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>36095.1781562173</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>35148.3586475934</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>36374.4770732898</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>34299.1887312282</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>35136.1494839467</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>38980.3641949664</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>41424.6006992877</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>47007.0857898274</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>48604.196370112</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>0.057</t>
+          <t>56999.5278244802</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>66478.4202078018</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>54199.730352849</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>4710.75539211148</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4212.1225937902</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>3997.26706717394</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4286.60356455404</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4305.69456928617</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>4662.67599658297</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4376.82787128729</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4478.81202152874</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>5189.95321622499</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>6725.66583568315</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>7379.73842167862</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>7844.2542365004</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>9014.97906100804</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>10154.3609320523</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>9323.4775199472</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>19572.3958581711</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>18925.4714281003</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>18568.7305878897</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>18331.2755329939</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>18112.9134678529</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>16566.5915432909</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>15770.2204550277</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>15930.848245914</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>18192.0577937013</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>21549.4472587756</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>23260.9299906322</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>26175.3367256515</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>32215.3206759872</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>33019.5235028792</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>23070.9206018441</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.603</t>
+          <t>603201.575486566</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.635</t>
+          <t>635044.512454601</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.637</t>
+          <t>637132.692268092</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>666934.611982756</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.717</t>
+          <t>716952.376449628</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.754</t>
+          <t>753803.205349431</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.751</t>
+          <t>751181.303721975</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.757</t>
+          <t>757360.84485949</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.825</t>
+          <t>824673.099342206</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.949</t>
+          <t>949221.452226363</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1060313.74320119</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>1.102</t>
+          <t>1102337.04437576</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>1.229</t>
+          <t>1228722.9212872</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>1.433</t>
+          <t>1432613.63749969</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>1.279</t>
+          <t>1279410.61069487</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2572.03516598435</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2561.98234325186</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2142.83520834723</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2270.61256770174</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2700.08400607167</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3138.09736214988</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2476.15702176446</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2604.06633454643</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2934.39853458804</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3106.31788743071</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3146.11159753236</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>3671.38830705246</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4115.74527258751</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>4700.53191300226</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>3869.68750097756</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,84 +3211,84 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>0.204</t>
+          <t>203932.528362678</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>210072.029946711</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0.192</t>
+          <t>192431.463565107</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>0.209</t>
+          <t>208757.098712788</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>0.231</t>
+          <t>230993.494904574</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>0.227</t>
+          <t>227183.614925591</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.227</t>
+          <t>227435.102035679</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.204</t>
+          <t>204363.699654061</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>0.265</t>
+          <t>264981.488166465</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0.299</t>
+          <t>298959.151964744</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>0.331</t>
+          <t>331121.67478089</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>0.348</t>
+          <t>347726.922324567</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>0.411</t>
+          <t>411088.958573294</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>0.462</t>
+          <t>461724.559542351</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>0.379</t>
+          <t>378955.813422554</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,84 +3298,84 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>0.393</t>
+          <t>392608.851160413</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>0.397</t>
+          <t>397459.334604282</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0.383</t>
+          <t>382954.752902019</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>0.377</t>
+          <t>377334.758020929</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>0.374</t>
+          <t>374072.308083116</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>379558.90106727</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.331</t>
+          <t>330705.022025713</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.321</t>
+          <t>320547.064502152</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>350221.18143249</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0.397</t>
+          <t>396724.745185446</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>0.441</t>
+          <t>440813.239788276</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>0.482</t>
+          <t>482425.04802816</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>0.577</t>
+          <t>576930.760792721</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>0.631</t>
+          <t>630612.041704561</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>0.544</t>
+          <t>543844.089307807</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,84 +3385,84 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>86260.383922573</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>0.085</t>
+          <t>85009.0459651843</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>77309.8270801986</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>0.081</t>
+          <t>80697.303003188</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>0.084</t>
+          <t>84125.727916321</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>0.092</t>
+          <t>91670.2857042445</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.089</t>
+          <t>89235.0520745345</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>88485.6522262759</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>96064.9172211226</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>110331.984757148</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>114465.925712906</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>0.122</t>
+          <t>121694.149558323</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>0.143</t>
+          <t>142696.870542448</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>0.162</t>
+          <t>162391.777677937</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>120421.232821684</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>170280.601212041</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>0.177</t>
+          <t>176792.574447604</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0.152</t>
+          <t>151503.35695343</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>0.136</t>
+          <t>136351.025063991</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>0.168</t>
+          <t>167900.580678609</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>0.163</t>
+          <t>163113.494745734</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.158</t>
+          <t>158085.626843946</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.147</t>
+          <t>147278.461677211</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>160365.266306306</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0.172</t>
+          <t>172357.086857313</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>0.183</t>
+          <t>182748.36048887</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>0.194</t>
+          <t>193753.611291603</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>0.223</t>
+          <t>223476.691898532</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>0.251</t>
+          <t>251014.904935761</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>0.224</t>
+          <t>223840.618993325</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2.083</t>
+          <t>2082710.53332397</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>2090201.45968434</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.933</t>
+          <t>1933122.98183586</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>1.804</t>
+          <t>1804089.2057495</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>1.742</t>
+          <t>1742380.13023402</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1810292.05291701</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>1.803</t>
+          <t>1803248.56198875</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>1.799</t>
+          <t>1798956.33432674</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>1.946</t>
+          <t>1946234.46272622</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>2.104</t>
+          <t>2103871.76006886</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2.238</t>
+          <t>2238298.09583973</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2289724.89554343</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>2.659</t>
+          <t>2658513.84216237</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>2.931</t>
+          <t>2931160.28961516</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>2.657</t>
+          <t>2657453.08192183</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>60999.6565528436</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>62016.4759997378</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>56430.9286861241</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>54570.3126324041</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>54118.8995247181</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>53498.6208693264</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>52287.6640299472</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>51339.9641244162</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>0.057</t>
+          <t>56678.1272922942</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>62618.0503003503</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>69719.5651778484</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>76560.7903990476</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>94702.9538188017</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>0.106</t>
+          <t>106392.953851068</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>0.094</t>
+          <t>94492.1321217319</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>25472.8067641516</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>24716.702524909</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>22887.3548821767</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>22897.2929675652</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>24052.7395055928</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>25349.1575992805</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>23982.1930341538</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>24622.0217030519</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>28278.6179875513</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>31208.9665044608</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>33206.8577200151</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>35964.9395269212</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>42298.1455941635</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>49767.3712761747</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>40828.4603465209</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,84 +3820,84 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>0.105</t>
+          <t>104930.521106513</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>0.102</t>
+          <t>102477.520177972</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0.098</t>
+          <t>98220.4754700023</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>0.101</t>
+          <t>101044.483610719</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>0.108</t>
+          <t>107529.122363379</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>118622.548771048</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>110440.906557909</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.111</t>
+          <t>110867.245852027</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>123355.269159887</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>139231.619992638</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>0.152</t>
+          <t>152398.292204725</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>0.162</t>
+          <t>161978.424334427</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>0.191</t>
+          <t>190637.536209238</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>0.194</t>
+          <t>193520.743054291</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>0.154</t>
+          <t>153979.521075511</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>0.334</t>
+          <t>333984.006337955</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>0.346</t>
+          <t>345869.689597967</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>360464.433761617</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>0.355</t>
+          <t>355109.907311466</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>0.379</t>
+          <t>378746.30783657</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>0.397</t>
+          <t>396883.400163224</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.366</t>
+          <t>365765.750307113</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.381</t>
+          <t>380719.88913226</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>0.438</t>
+          <t>437565.017308534</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0.498</t>
+          <t>497613.882766105</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>0.553</t>
+          <t>552868.773468126</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>0.581</t>
+          <t>580680.043028901</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>0.662</t>
+          <t>662436.274041161</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>0.764</t>
+          <t>763596.495707922</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>0.613</t>
+          <t>612597.623315582</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>310058.140963509</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>0.307</t>
+          <t>306766.118916639</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0.301</t>
+          <t>301188.936233414</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>0.296</t>
+          <t>295660.212640803</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>0.314</t>
+          <t>313988.178485422</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>0.346</t>
+          <t>346187.034422207</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0.308</t>
+          <t>307772.812756257</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0.335</t>
+          <t>334580.2208395</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>0.378</t>
+          <t>377919.590856462</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>0.458</t>
+          <t>458478.868585133</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>0.482</t>
+          <t>482124.285658615</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>519806.78294163</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>0.588</t>
+          <t>588056.270815087</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>0.654</t>
+          <t>654198.153995813</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>0.523</t>
+          <t>523017.653114637</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>3.005</t>
+          <t>3005104.24557771</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>3029728.67482594</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>3.015</t>
+          <t>3015064.70670337</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>3.046</t>
+          <t>3046085.17708483</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>3.232</t>
+          <t>3232344.53931518</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>3.435</t>
+          <t>3435034.14423214</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>3200234.23955804</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>3.136</t>
+          <t>3136281.67615818</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>3.381</t>
+          <t>3380988.77803731</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>3.877</t>
+          <t>3876669.44267631</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>4.264</t>
+          <t>4263810.92140011</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>4.553</t>
+          <t>4553265.30908434</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>5.006</t>
+          <t>5006497.10582246</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>5.487</t>
+          <t>5486820.8693764</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>4400016.37590637</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>19.16</t>
+          <t>19160130.5296985</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>19.836</t>
+          <t>19836491.3151498</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>20.316</t>
+          <t>20316151.9456063</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>20.446</t>
+          <t>20445905.8756702</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>21.221</t>
+          <t>21221237.8948146</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>22.317</t>
+          <t>22316756.6076057</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>22.551</t>
+          <t>22551155.4178981</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>23.974</t>
+          <t>23973800.35025</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>26.917</t>
+          <t>26917247.6147694</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>30.746</t>
+          <t>30745623.5528469</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>33.821</t>
+          <t>33821453.3239725</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>36.961</t>
+          <t>36961322.5797225</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>41.918</t>
+          <t>41917579.7971936</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>47.233</t>
+          <t>47233025.61079</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>45.785</t>
+          <t>45785146.8034092</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>55.182</t>
+          <t>55182308.5366997</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>56.556</t>
+          <t>56556389.0503581</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>56.599</t>
+          <t>56598550.2992956</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>56.061</t>
+          <t>56060688.4328249</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>58.306</t>
+          <t>58306395.8341117</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>60.817</t>
+          <t>60817361.9019018</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>60.203</t>
+          <t>60202725.9733039</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>62.264</t>
+          <t>62263778.5854962</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>70.209</t>
+          <t>70209291.8668545</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>79.624</t>
+          <t>79623724.2735859</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>87.526</t>
+          <t>87525633.878685</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>95.929</t>
+          <t>95929115.303749</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>109.398</t>
+          <t>109397506.893586</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>122.789</t>
+          <t>122789481.799158</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>114.158</t>
+          <t>114158105.32809</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4339,7 +4344,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4351,7 +4356,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4363,7 +4368,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4375,7 +4380,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4387,7 +4392,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4399,7 +4404,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4411,7 +4416,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4423,7 +4428,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4470,6 +4475,11 @@
           <t>gross_output.s.du</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4504,6 +4514,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 2</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpA2</t>
